--- a/data/datasets.xlsx
+++ b/data/datasets.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10402"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kokul/Projects/GOMAP-enrich/app/static/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kokul/Projects/GOMAP-enrich/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F32603A9-A116-6740-B27A-D4395EB87612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90B9C563-4FEC-264F-AA4F-C56A553031A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{E467A60D-F69A-4F4A-9E6E-FC569BD129C9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="277">
   <si>
     <t>Species</t>
   </si>
@@ -56,23 +57,836 @@
     <t>maize.B73.AGPv4.aggregate.gaf.gz</t>
   </si>
   <si>
-    <t>3.1_Zea_mays_B73.MaizeGDB.CLEANED.gaf.gz</t>
-  </si>
-  <si>
-    <t>B73_v5</t>
+    <t>ASM31485v2</t>
+  </si>
+  <si>
+    <t>Annotation</t>
+  </si>
+  <si>
+    <t>Common_name</t>
+  </si>
+  <si>
+    <t>Maize</t>
+  </si>
+  <si>
+    <t>Banana</t>
+  </si>
+  <si>
+    <t>Musa acuminata</t>
+  </si>
+  <si>
+    <t>ASM31485v2_Dec_2022</t>
+  </si>
+  <si>
+    <t>ASM31485v2_Feb_2021</t>
+  </si>
+  <si>
+    <t>Barley</t>
+  </si>
+  <si>
+    <t>Hordeum vulgare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBSC Morex v1 </t>
+  </si>
+  <si>
+    <t>Barley_IBSC_PGSB-1.0_May_2019.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>Banana_NCBI_ASM31385v2_February_2021.r1.gaf.gz.gz</t>
+  </si>
+  <si>
+    <t>Banana_NCBI_ASM31385v2_December_2022_v2.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Morex V3 </t>
+  </si>
+  <si>
+    <t>Barley_IPK_cv_Morex_V3_June_2023_v1.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>Barrel Clover</t>
+  </si>
+  <si>
+    <t>Medicago truncatula</t>
+  </si>
+  <si>
+    <t>BarrelClover_A17_HM341_Mt4.0v2_August_2019.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>Line</t>
+  </si>
+  <si>
+    <t>B73</t>
+  </si>
+  <si>
+    <t>Morex</t>
+  </si>
+  <si>
+    <t>R108</t>
+  </si>
+  <si>
+    <t>A17</t>
+  </si>
+  <si>
+    <t>BarrelClover_R108_HM340_v1.0_August_2019.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>Dec_2022</t>
+  </si>
+  <si>
+    <t>Feb_2021</t>
+  </si>
+  <si>
+    <t>PGSB</t>
+  </si>
+  <si>
+    <t>medtr.A17_HM341.gnm4.ann2.G3ZY</t>
+  </si>
+  <si>
+    <t>R108_HM340.gnm1.ann1.85YW</t>
+  </si>
+  <si>
+    <t>gnm4.ann2</t>
+  </si>
+  <si>
+    <t>gnm1.ann1</t>
+  </si>
+  <si>
+    <t>medtr.A17.gnm5.ann1_6.L2RX</t>
+  </si>
+  <si>
+    <t>Barrel_Clover_LIS_R108.gnmHiC_1.ann1.Y8NH_November_2022_v1.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>Barrel_Clover_LIS_A17.gnm5.ann1_6.L2RX_November_2022_v1.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>Brachypodium distachyon</t>
+  </si>
+  <si>
+    <t>Stiff Brome</t>
+  </si>
+  <si>
+    <t>Bd21</t>
+  </si>
+  <si>
+    <t>Bd21.v3.1</t>
+  </si>
+  <si>
+    <t>v3.1</t>
+  </si>
+  <si>
+    <t>Bdistachyon.Bd21.v3.1_November_2019.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>Vaccinium corymbosum</t>
+  </si>
+  <si>
+    <t>American Blueberry</t>
+  </si>
+  <si>
+    <t>Draper</t>
+  </si>
+  <si>
+    <t>Draper_v1.0</t>
+  </si>
+  <si>
+    <t>v1.0</t>
+  </si>
+  <si>
+    <t>Blueberry_GigaDB_Draper_v1.0_May_2023_v2.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>Theobroma cacao</t>
+  </si>
+  <si>
+    <t>Cacao</t>
+  </si>
+  <si>
+    <t>B97-61/B2</t>
+  </si>
+  <si>
+    <t>Criollo_cocoa_genome_V2</t>
+  </si>
+  <si>
+    <t>GCF_000208745.1</t>
+  </si>
+  <si>
+    <t>Cacao_NCBI_CriolloV2_December_2022_v2.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>Cannabis sativa</t>
+  </si>
+  <si>
+    <t>Hemp</t>
+  </si>
+  <si>
+    <t>CBDRx-18</t>
+  </si>
+  <si>
+    <t>GCF_900626175.2</t>
+  </si>
+  <si>
+    <t>Brassica napus</t>
+  </si>
+  <si>
+    <t>ZS11</t>
+  </si>
+  <si>
+    <t>ZS11-v0</t>
+  </si>
+  <si>
+    <t>v0</t>
+  </si>
+  <si>
+    <t>Coffea canephora</t>
+  </si>
+  <si>
+    <t>Coffee</t>
+  </si>
+  <si>
+    <t>Coffee_CGH_v1.0_May_2023_v2.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>DH200=94</t>
+  </si>
+  <si>
+    <t>phavu.G19833.gnm2.ann1.PB8d</t>
+  </si>
+  <si>
+    <t>G19833</t>
+  </si>
+  <si>
+    <t>gnm2.ann1</t>
+  </si>
+  <si>
+    <t>Common Bean</t>
+  </si>
+  <si>
+    <t>Phaseolus vulgaris</t>
+  </si>
+  <si>
+    <t>CommonBean_LIS_G19833_November_2022_v2.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>Gossypium raimondii</t>
+  </si>
+  <si>
+    <t>Cotton</t>
+  </si>
+  <si>
+    <t>v2.0</t>
+  </si>
+  <si>
+    <t>Cotton_DOE-JGI_v2.1_June_2023_v2.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>Cowpea_JGI_IT97K-499-35_December_2022_v1.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>Vigna unguiculata</t>
+  </si>
+  <si>
+    <t>IT97K-499-35.gnm1.ann2.FD7K</t>
+  </si>
+  <si>
+    <t>IT97K-499-35</t>
+  </si>
+  <si>
+    <t>gnm1.ann2</t>
+  </si>
+  <si>
+    <t>Cowpea</t>
+  </si>
+  <si>
+    <t>Vitis vinifera</t>
+  </si>
+  <si>
+    <t>Wine Grape</t>
+  </si>
+  <si>
+    <t>PN40024</t>
+  </si>
+  <si>
+    <t>PN40024-12X</t>
+  </si>
+  <si>
+    <t>12x</t>
+  </si>
+  <si>
+    <t>Grape_Genoscope_12x_May_2023_v2.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>Cannabis_NCBI_cs10_2.0_October_2022_v1.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>Humulus lupulus</t>
+  </si>
+  <si>
+    <t>Hop</t>
+  </si>
+  <si>
+    <t>Cascade</t>
+  </si>
+  <si>
+    <t>Hop_HopBase_Cascade_July_2023_v2.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>Zm-Mo17-REFERENCE-CAU-2.0</t>
+  </si>
+  <si>
+    <t>Zm00014ba</t>
+  </si>
+  <si>
+    <t>Maize_CyVerse_Mo17_CAU_2.0_July_2023.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>Maize_MaizeGDB_B73_NAM_5.0_October_2022_v2.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>Zm00001eb</t>
+  </si>
+  <si>
+    <t>B97-REFERENCE-NAM-1.0_Zm00018ab</t>
+  </si>
+  <si>
+    <t>B73-REFERENCE-NAM-5.0_Zm00001eb</t>
+  </si>
+  <si>
+    <t>Mo17-REFERENCE-CAU-2.0_Zm00014ba</t>
+  </si>
+  <si>
+    <t>Zm00018ab</t>
+  </si>
+  <si>
+    <t>CML52-REFERENCE-NAM-1.0_Zm00019ab</t>
+  </si>
+  <si>
+    <t>B37</t>
+  </si>
+  <si>
+    <t>CML52</t>
+  </si>
+  <si>
+    <t>Zm00019ab</t>
+  </si>
+  <si>
+    <t>CML228</t>
+  </si>
+  <si>
+    <t>CML247</t>
+  </si>
+  <si>
+    <t>CML277</t>
+  </si>
+  <si>
+    <t>CML322</t>
+  </si>
+  <si>
+    <t>CML333</t>
+  </si>
+  <si>
+    <t>CML69</t>
+  </si>
+  <si>
+    <t>HP301</t>
+  </si>
+  <si>
+    <t>Il14H</t>
+  </si>
+  <si>
+    <t>Ki11</t>
+  </si>
+  <si>
+    <t>Ki3</t>
+  </si>
+  <si>
+    <t>Ky21</t>
+  </si>
+  <si>
+    <t>M162W</t>
+  </si>
+  <si>
+    <t>M37W</t>
+  </si>
+  <si>
+    <t>Mo17</t>
+  </si>
+  <si>
+    <t>Mo18W</t>
+  </si>
+  <si>
+    <t>Ms71</t>
+  </si>
+  <si>
+    <t>NC350</t>
+  </si>
+  <si>
+    <t>NC358</t>
+  </si>
+  <si>
+    <t>Oh43</t>
+  </si>
+  <si>
+    <t>Oh7B</t>
+  </si>
+  <si>
+    <t>P39</t>
+  </si>
+  <si>
+    <t>PH207</t>
+  </si>
+  <si>
+    <t>Tx303</t>
+  </si>
+  <si>
+    <t>Tzi8</t>
+  </si>
+  <si>
+    <t>W22</t>
+  </si>
+  <si>
+    <t>CML103</t>
+  </si>
+  <si>
+    <t>CML103-REFERENCE-NAM-1.0_Zm00021ab</t>
+  </si>
+  <si>
+    <t>Zm00021ab</t>
+  </si>
+  <si>
+    <t>CML228-REFERENCE-NAM-1.0_Zm00022ab</t>
+  </si>
+  <si>
+    <t>Zm00022ab</t>
+  </si>
+  <si>
+    <t>CML247-REFERENCE-NAM-1.0_Zm00023ab</t>
+  </si>
+  <si>
+    <t>Zm00023ab</t>
+  </si>
+  <si>
+    <t>Maize_MaizeGDB_B97_NAM_1.0_October_2022.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>Maize_MaizeGDB_CML52_NAM_1.0_November_2022.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>Maize_MaizeGDB_CML103_NAM_1.0_October_2022.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>Maize_MaizeGDB_CML228_NAM_1.0_October_2022.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>Maize_MaizeGDB_CML247_NAM_1.0_October_2022.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>Zm00024ab</t>
+  </si>
+  <si>
+    <t>CML277-REFERENCE-NAM-1.0_Zm00024ab</t>
+  </si>
+  <si>
+    <t>Maize_MaizeGDB_CML277_NAM_1.0_October_2022.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>CML322-REFERENCE-NAM-1.0_Zm00025ab</t>
+  </si>
+  <si>
+    <t>Zm00025ab</t>
+  </si>
+  <si>
+    <t>Maize_MaizeGDB_CML322_NAM_1.0_November_2022.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>Maize_MaizeGDB_CML333_NAM_1.0_November_2022.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>CML333-REFERENCE-NAM-1.0_Zm00026ab</t>
+  </si>
+  <si>
+    <t>Zm00026ab</t>
+  </si>
+  <si>
+    <t>Maize_MaizeGDB_CML69_NAM_1.0_November_2022.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>CML69-REFERENCE-NAM-1.0_Zm00020ab</t>
+  </si>
+  <si>
+    <t>Zm00020ab</t>
+  </si>
+  <si>
+    <t>Maize_MaizeGDB_HP301_NAM_1.0_November_2022.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>HP301-REFERENCE-NAM-1.0_Zm00027ab</t>
+  </si>
+  <si>
+    <t>Zm00027ab</t>
+  </si>
+  <si>
+    <t>Maize_MaizeGDB_Il14H_NAM_1.0_November_2022.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>Il14H-REFERENCE-NAM-1.0_Zm00028ab</t>
+  </si>
+  <si>
+    <t>Zm00028ab</t>
+  </si>
+  <si>
+    <t>Maize_MaizeGDB_Ki11_NAM_1.0_November_2022.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>Zm-Ki11-REFERENCE-NAM-1.0_Zm00030ab</t>
+  </si>
+  <si>
+    <t>Zm00030ab</t>
+  </si>
+  <si>
+    <t>Maize_MaizeGDB_Ki3_NAM_1.0_November_2022.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>Ki3-REFERENCE-NAM-1.0_Zm00029ab</t>
+  </si>
+  <si>
+    <t>Zm00029ab</t>
+  </si>
+  <si>
+    <t>Maize_MaizeGDB_Ky21_NAM_1.0_November_2022.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>Ky21-REFERENCE-NAM-1.0_Zm00031ab</t>
+  </si>
+  <si>
+    <t>Zm00031ab</t>
+  </si>
+  <si>
+    <t>Maize_MaizeGDB_M162W_NAM_1.0_November_2022.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>M162W-REFERENCE-NAM-1.0_Zm00033ab</t>
+  </si>
+  <si>
+    <t>Zm00033ab</t>
+  </si>
+  <si>
+    <t>Maize_MaizeGDB_M37W_NAM_1.0_November_2022.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>M37W-REFERENCE-NAM-1.0_Zm00032ab</t>
+  </si>
+  <si>
+    <t>Zm00032ab</t>
+  </si>
+  <si>
+    <t>Maize_MaizeGDB_Mo17_CAU_1.0_May_2023_v2.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>Mo17-REFERENCE-CAU-1.0_Zm00014a</t>
+  </si>
+  <si>
+    <t>Zm00014a</t>
+  </si>
+  <si>
+    <t>Maize_MaizeGDB_Mo18W_NAM_1.0_November_2022.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>Mo18W-REFERENCE-NAM-1.0_Zm00034ab</t>
+  </si>
+  <si>
+    <t>Zm00034ab</t>
+  </si>
+  <si>
+    <t>Maize_MaizeGDB_Ms71_NAM_1.0_November_2022.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>Ms71-REFERENCE-NAM-1.0_Zm00035ab</t>
+  </si>
+  <si>
+    <t>Zm00035ab</t>
+  </si>
+  <si>
+    <t>Maize_MaizeGDB_NC350_NAM_1.0_November_2022.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>NC350-REFERENCE-NAM-1.0_Zm00036ab</t>
+  </si>
+  <si>
+    <t>Zm00036ab</t>
+  </si>
+  <si>
+    <t>Maize_MaizeGDB_NC358_NAM_1.0_November_2022.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>NC358-REFERENCE-NAM-1.0_Zm00037ab</t>
+  </si>
+  <si>
+    <t>Zm00037ab</t>
+  </si>
+  <si>
+    <t>Maize_MaizeGDB_Oh43_NAM_1.0_November_2022.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>Oh43-REFERENCE-NAM-1.0_Zm00039ab</t>
+  </si>
+  <si>
+    <t>Zm00039ab</t>
+  </si>
+  <si>
+    <t>Maize_MaizeGDB_Oh7B_NAM_1.0_November_2022.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>Oh7B-REFERENCE-NAM-1.0_Zm00038ab</t>
+  </si>
+  <si>
+    <t>Zm00038ab</t>
+  </si>
+  <si>
+    <t>Maize_MaizeGDB_P39_NAM_1.0_November_2022.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>P39-REFERENCE-NAM-1.0_Zm00040ab</t>
+  </si>
+  <si>
+    <t>Zm00040ab</t>
+  </si>
+  <si>
+    <t>Maize_MaizeGDB_PH207_NS-UIUC_UMN_1.0_May_2023_v2.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>PH207-REFERENCE_NS-UIUC_UMN-1.0_Zm00008a</t>
+  </si>
+  <si>
+    <t>Zm00008a</t>
+  </si>
+  <si>
+    <t>Maize_MaizeGDB_Tx303_NAM_1.0_November_2022.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>Tx303-REFERENCE-NAM-1.0_Zm00041ab</t>
+  </si>
+  <si>
+    <t>Zm00041ab</t>
+  </si>
+  <si>
+    <t>Maize_MaizeGDB_Tzi8_NAM_1.0_November_2022.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>Tzi8-REFERENCE-NAM-1.0_Zm00042ab</t>
+  </si>
+  <si>
+    <t>Zm00042ab</t>
+  </si>
+  <si>
+    <t>Maize_MaizeGDB_W22_NRGENE_2.0_May_2023_v2.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>W22-REFERENCE-NRGENE-2.0_Zm00004b</t>
+  </si>
+  <si>
+    <t>Zm00004b</t>
+  </si>
+  <si>
+    <t>Arachis hypogaea</t>
+  </si>
+  <si>
+    <t>Peanut</t>
+  </si>
+  <si>
+    <t>Tifrunner.gnm2.ann1.4K0L</t>
+  </si>
+  <si>
+    <t>gnm2.ann1.4K0L</t>
+  </si>
+  <si>
+    <t>Peanut_Tifrunner.IPGI.2.0_November_2022_v1.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>Pepper_PGP_cvCM334_June_2023_v2.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>Pepper</t>
+  </si>
+  <si>
+    <t>Capsicum annuum</t>
+  </si>
+  <si>
+    <t>CM334</t>
+  </si>
+  <si>
+    <t>Tifrunner</t>
+  </si>
+  <si>
+    <t>PGAv.1.6</t>
+  </si>
+  <si>
+    <t>CM334-PGAv.1.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oilseed rape </t>
+  </si>
+  <si>
+    <t>Rapeseed_BnPIR_ZS11_June_2023_v2.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>Rice_IRGSP_1.0_June_2023_v2.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>Rice</t>
+  </si>
+  <si>
+    <t>Oryza sativa japonica</t>
+  </si>
+  <si>
+    <t>IRGSP-1.0</t>
+  </si>
+  <si>
+    <t>Nipponbare</t>
+  </si>
+  <si>
+    <t>ITAG4.1</t>
+  </si>
+  <si>
+    <t>SL4.0-ITAG4.1</t>
+  </si>
+  <si>
+    <t>Heinz 1706</t>
+  </si>
+  <si>
+    <t>Solanum lycopersicum</t>
+  </si>
+  <si>
+    <t>Tomato</t>
+  </si>
+  <si>
+    <t>LA0716</t>
+  </si>
+  <si>
+    <t>Solanum pennellii</t>
+  </si>
+  <si>
+    <t>Wild Tomato</t>
+  </si>
+  <si>
+    <t>spenn_v2.0</t>
+  </si>
+  <si>
+    <t>Sorghum_DOE-JGI_v3.1.1_March_2023_v1.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>v3.1.1</t>
+  </si>
+  <si>
+    <t>v3.0-v3.1.1</t>
+  </si>
+  <si>
+    <t>BTx623</t>
+  </si>
+  <si>
+    <t>Sorghum bicolor</t>
+  </si>
+  <si>
+    <t>Sorghum</t>
+  </si>
+  <si>
+    <t>Soybean_LIS_Wm82_IGA1008.gnm1.ann1.FGN6_May_2023_v1.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>Glycine Max</t>
+  </si>
+  <si>
+    <t>Soybean</t>
+  </si>
+  <si>
+    <t>Wm82.a4.v1</t>
+  </si>
+  <si>
+    <t>Williams 82</t>
+  </si>
+  <si>
+    <t>gnm4.ann1</t>
+  </si>
+  <si>
+    <t>Zm00001d</t>
+  </si>
+  <si>
+    <t>Stiff_brome_DOE-JGI_Bd21_v3.2_May_2023_v1.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>v3.2</t>
+  </si>
+  <si>
+    <t>v3.0-v3.2</t>
+  </si>
+  <si>
+    <t>Sugar_Pine_TreeGenes_v1.5_June_2023_v2.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>Sugar Pine</t>
+  </si>
+  <si>
+    <t>Pinus lambertiana</t>
+  </si>
+  <si>
+    <t>v1.5</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Tea_Teabase_CSS_ChrLev_20200506_June_2023_v1.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>Tea</t>
+  </si>
+  <si>
+    <t>Camellia sinensis</t>
+  </si>
+  <si>
+    <t>Shuchazao</t>
+  </si>
+  <si>
+    <t>Tomato_SGN_SL4.0_July_2023_v2.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>Wheat_URGI_IWGSC_RefSeq_v2.1_May_2023_v1.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>Triticum aestivum</t>
+  </si>
+  <si>
+    <t>Wheat</t>
+  </si>
+  <si>
+    <t>v2.1</t>
+  </si>
+  <si>
+    <t>Chinese Spring</t>
+  </si>
+  <si>
+    <t>Wild_Tomato_SGN_LA716_June_2023_v2.r1.gaf.gz</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Lucida Grande"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -95,8 +909,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -431,43 +1246,2377 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DBB0A96-91CA-984C-B37F-8D25BAD45885}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="39.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.1640625" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="64.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="59.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
+      <c r="C1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" t="s">
+        <v>257</v>
+      </c>
+      <c r="F2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" t="s">
+        <v>56</v>
+      </c>
+      <c r="E7" t="s">
+        <v>57</v>
+      </c>
+      <c r="F7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" t="s">
+        <v>62</v>
+      </c>
+      <c r="F8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9" t="s">
+        <v>70</v>
+      </c>
+      <c r="E9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>74</v>
+      </c>
+      <c r="B10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C10" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" t="s">
+        <v>71</v>
+      </c>
+      <c r="E10" t="s">
+        <v>73</v>
+      </c>
+      <c r="F10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>78</v>
+      </c>
+      <c r="B11" t="s">
+        <v>77</v>
+      </c>
+      <c r="D11" t="s">
+        <v>79</v>
+      </c>
+      <c r="E11" t="s">
+        <v>79</v>
+      </c>
+      <c r="F11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>86</v>
+      </c>
+      <c r="B12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C12" t="s">
+        <v>84</v>
+      </c>
+      <c r="D12" t="s">
+        <v>83</v>
+      </c>
+      <c r="E12" t="s">
+        <v>85</v>
+      </c>
+      <c r="F12" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>88</v>
+      </c>
+      <c r="B13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D13" t="s">
+        <v>90</v>
+      </c>
+      <c r="E13" t="s">
+        <v>91</v>
+      </c>
+      <c r="F13" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>95</v>
+      </c>
+      <c r="B14" t="s">
+        <v>94</v>
+      </c>
+      <c r="C14" t="s">
+        <v>96</v>
+      </c>
+      <c r="D14" t="s">
+        <v>96</v>
+      </c>
+      <c r="E14" t="s">
+        <v>96</v>
+      </c>
+      <c r="F14" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" t="s">
+        <v>98</v>
+      </c>
+      <c r="D15" t="s">
+        <v>105</v>
+      </c>
+      <c r="E15" t="s">
+        <v>99</v>
+      </c>
+      <c r="F15" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" t="s">
+        <v>104</v>
+      </c>
+      <c r="E16" t="s">
+        <v>102</v>
+      </c>
+      <c r="F16" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" t="s">
+        <v>108</v>
+      </c>
+      <c r="D17" t="s">
+        <v>103</v>
+      </c>
+      <c r="E17" t="s">
+        <v>106</v>
+      </c>
+      <c r="F17" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" t="s">
+        <v>136</v>
+      </c>
+      <c r="D18" t="s">
+        <v>137</v>
+      </c>
+      <c r="E18" t="s">
+        <v>138</v>
+      </c>
+      <c r="F18" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D19" t="s">
+        <v>139</v>
+      </c>
+      <c r="E19" t="s">
+        <v>140</v>
+      </c>
+      <c r="F19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" t="s">
+        <v>112</v>
+      </c>
+      <c r="D20" t="s">
+        <v>141</v>
+      </c>
+      <c r="E20" t="s">
+        <v>142</v>
+      </c>
+      <c r="F20" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" t="s">
+        <v>113</v>
+      </c>
+      <c r="D21" t="s">
+        <v>149</v>
+      </c>
+      <c r="E21" t="s">
+        <v>148</v>
+      </c>
+      <c r="F21" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" t="s">
+        <v>114</v>
+      </c>
+      <c r="D22" t="s">
+        <v>151</v>
+      </c>
+      <c r="E22" t="s">
+        <v>152</v>
+      </c>
+      <c r="F22" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1</v>
+      </c>
+      <c r="C23" t="s">
+        <v>115</v>
+      </c>
+      <c r="D23" t="s">
+        <v>155</v>
+      </c>
+      <c r="E23" t="s">
+        <v>156</v>
+      </c>
+      <c r="F23" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" t="s">
+        <v>109</v>
+      </c>
+      <c r="D24" t="s">
+        <v>107</v>
+      </c>
+      <c r="E24" t="s">
+        <v>110</v>
+      </c>
+      <c r="F24" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C25" t="s">
+        <v>116</v>
+      </c>
+      <c r="D25" t="s">
+        <v>158</v>
+      </c>
+      <c r="E25" t="s">
+        <v>159</v>
+      </c>
+      <c r="F25" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C26" t="s">
+        <v>117</v>
+      </c>
+      <c r="D26" t="s">
+        <v>161</v>
+      </c>
+      <c r="E26" t="s">
+        <v>162</v>
+      </c>
+      <c r="F26" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1</v>
+      </c>
+      <c r="C27" t="s">
+        <v>118</v>
+      </c>
+      <c r="D27" t="s">
+        <v>164</v>
+      </c>
+      <c r="E27" t="s">
+        <v>165</v>
+      </c>
+      <c r="F27" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" t="s">
+        <v>119</v>
+      </c>
+      <c r="D28" t="s">
+        <v>167</v>
+      </c>
+      <c r="E28" t="s">
+        <v>168</v>
+      </c>
+      <c r="F28" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" t="s">
+        <v>1</v>
+      </c>
+      <c r="C29" t="s">
+        <v>120</v>
+      </c>
+      <c r="D29" t="s">
+        <v>170</v>
+      </c>
+      <c r="E29" t="s">
+        <v>171</v>
+      </c>
+      <c r="F29" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" t="s">
+        <v>1</v>
+      </c>
+      <c r="C30" t="s">
+        <v>121</v>
+      </c>
+      <c r="D30" t="s">
+        <v>173</v>
+      </c>
+      <c r="E30" t="s">
+        <v>174</v>
+      </c>
+      <c r="F30" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1</v>
+      </c>
+      <c r="C31" t="s">
+        <v>122</v>
+      </c>
+      <c r="D31" t="s">
+        <v>176</v>
+      </c>
+      <c r="E31" t="s">
+        <v>177</v>
+      </c>
+      <c r="F31" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" t="s">
+        <v>1</v>
+      </c>
+      <c r="C32" t="s">
+        <v>123</v>
+      </c>
+      <c r="D32" t="s">
+        <v>179</v>
+      </c>
+      <c r="E32" t="s">
+        <v>180</v>
+      </c>
+      <c r="F32" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C33" t="s">
+        <v>124</v>
+      </c>
+      <c r="D33" t="s">
+        <v>182</v>
+      </c>
+      <c r="E33" t="s">
+        <v>183</v>
+      </c>
+      <c r="F33" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C34" t="s">
+        <v>125</v>
+      </c>
+      <c r="D34" t="s">
+        <v>185</v>
+      </c>
+      <c r="E34" t="s">
+        <v>186</v>
+      </c>
+      <c r="F34" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>9</v>
+      </c>
+      <c r="B35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C35" t="s">
+        <v>126</v>
+      </c>
+      <c r="D35" t="s">
+        <v>188</v>
+      </c>
+      <c r="E35" t="s">
+        <v>189</v>
+      </c>
+      <c r="F35" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1</v>
+      </c>
+      <c r="C36" t="s">
+        <v>127</v>
+      </c>
+      <c r="D36" t="s">
+        <v>191</v>
+      </c>
+      <c r="E36" t="s">
+        <v>192</v>
+      </c>
+      <c r="F36" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1</v>
+      </c>
+      <c r="C37" t="s">
+        <v>128</v>
+      </c>
+      <c r="D37" t="s">
+        <v>194</v>
+      </c>
+      <c r="E37" t="s">
+        <v>195</v>
+      </c>
+      <c r="F37" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>9</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1</v>
+      </c>
+      <c r="C38" t="s">
+        <v>129</v>
+      </c>
+      <c r="D38" t="s">
+        <v>197</v>
+      </c>
+      <c r="E38" t="s">
+        <v>198</v>
+      </c>
+      <c r="F38" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>9</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C39" t="s">
+        <v>130</v>
+      </c>
+      <c r="D39" t="s">
+        <v>200</v>
+      </c>
+      <c r="E39" t="s">
+        <v>201</v>
+      </c>
+      <c r="F39" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>9</v>
+      </c>
+      <c r="B40" t="s">
+        <v>1</v>
+      </c>
+      <c r="C40" t="s">
+        <v>131</v>
+      </c>
+      <c r="D40" t="s">
+        <v>203</v>
+      </c>
+      <c r="E40" t="s">
+        <v>204</v>
+      </c>
+      <c r="F40" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>9</v>
+      </c>
+      <c r="B41" t="s">
+        <v>1</v>
+      </c>
+      <c r="C41" t="s">
+        <v>132</v>
+      </c>
+      <c r="D41" t="s">
+        <v>206</v>
+      </c>
+      <c r="E41" t="s">
+        <v>207</v>
+      </c>
+      <c r="F41" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>9</v>
+      </c>
+      <c r="B42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C42" t="s">
+        <v>133</v>
+      </c>
+      <c r="D42" t="s">
+        <v>209</v>
+      </c>
+      <c r="E42" t="s">
+        <v>210</v>
+      </c>
+      <c r="F42" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>9</v>
+      </c>
+      <c r="B43" t="s">
+        <v>1</v>
+      </c>
+      <c r="C43" t="s">
+        <v>134</v>
+      </c>
+      <c r="D43" t="s">
+        <v>212</v>
+      </c>
+      <c r="E43" t="s">
+        <v>213</v>
+      </c>
+      <c r="F43" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>9</v>
+      </c>
+      <c r="B44" t="s">
+        <v>1</v>
+      </c>
+      <c r="C44" t="s">
+        <v>135</v>
+      </c>
+      <c r="D44" t="s">
+        <v>215</v>
+      </c>
+      <c r="E44" t="s">
+        <v>216</v>
+      </c>
+      <c r="F44" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>218</v>
+      </c>
+      <c r="B45" t="s">
+        <v>217</v>
+      </c>
+      <c r="C45" t="s">
+        <v>226</v>
+      </c>
+      <c r="D45" t="s">
+        <v>219</v>
+      </c>
+      <c r="E45" t="s">
+        <v>220</v>
+      </c>
+      <c r="F45" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>223</v>
+      </c>
+      <c r="B46" t="s">
+        <v>224</v>
+      </c>
+      <c r="C46" t="s">
+        <v>225</v>
+      </c>
+      <c r="D46" t="s">
+        <v>228</v>
+      </c>
+      <c r="E46" t="s">
+        <v>227</v>
+      </c>
+      <c r="F46" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>229</v>
+      </c>
+      <c r="B47" t="s">
+        <v>63</v>
+      </c>
+      <c r="C47" t="s">
+        <v>64</v>
+      </c>
+      <c r="D47" t="s">
+        <v>65</v>
+      </c>
+      <c r="E47" t="s">
+        <v>66</v>
+      </c>
+      <c r="F47" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>232</v>
+      </c>
+      <c r="B48" t="s">
+        <v>233</v>
+      </c>
+      <c r="C48" t="s">
+        <v>235</v>
+      </c>
+      <c r="D48" t="s">
+        <v>234</v>
+      </c>
+      <c r="E48" t="s">
+        <v>234</v>
+      </c>
+      <c r="F48" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>250</v>
+      </c>
+      <c r="B49" t="s">
+        <v>249</v>
+      </c>
+      <c r="C49" t="s">
+        <v>248</v>
+      </c>
+      <c r="D49" t="s">
+        <v>247</v>
+      </c>
+      <c r="E49" t="s">
+        <v>246</v>
+      </c>
+      <c r="F49" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>253</v>
+      </c>
+      <c r="B50" t="s">
+        <v>252</v>
+      </c>
+      <c r="C50" t="s">
+        <v>255</v>
+      </c>
+      <c r="D50" t="s">
+        <v>254</v>
+      </c>
+      <c r="E50" t="s">
+        <v>256</v>
+      </c>
+      <c r="F50" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>42</v>
+      </c>
+      <c r="B51" t="s">
+        <v>41</v>
+      </c>
+      <c r="C51" t="s">
+        <v>43</v>
+      </c>
+      <c r="D51" t="s">
+        <v>260</v>
+      </c>
+      <c r="E51" t="s">
+        <v>259</v>
+      </c>
+      <c r="F51" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>262</v>
+      </c>
+      <c r="B52" t="s">
+        <v>263</v>
+      </c>
+      <c r="C52" t="s">
+        <v>265</v>
+      </c>
+      <c r="D52" t="s">
+        <v>264</v>
+      </c>
+      <c r="E52" t="s">
+        <v>264</v>
+      </c>
+      <c r="F52" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>267</v>
+      </c>
+      <c r="B53" t="s">
+        <v>268</v>
+      </c>
+      <c r="C53" t="s">
+        <v>269</v>
+      </c>
+      <c r="F53" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>240</v>
+      </c>
+      <c r="B54" t="s">
+        <v>239</v>
+      </c>
+      <c r="C54" t="s">
+        <v>238</v>
+      </c>
+      <c r="D54" t="s">
+        <v>237</v>
+      </c>
+      <c r="E54" t="s">
+        <v>236</v>
+      </c>
+      <c r="F54" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>273</v>
+      </c>
+      <c r="B55" t="s">
+        <v>272</v>
+      </c>
+      <c r="C55" t="s">
+        <v>275</v>
+      </c>
+      <c r="D55" t="s">
+        <v>274</v>
+      </c>
+      <c r="E55" t="s">
+        <v>274</v>
+      </c>
+      <c r="F55" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>243</v>
+      </c>
+      <c r="B56" t="s">
+        <v>242</v>
+      </c>
+      <c r="C56" t="s">
+        <v>241</v>
+      </c>
+      <c r="D56" t="s">
+        <v>244</v>
+      </c>
+      <c r="E56" t="s">
+        <v>244</v>
+      </c>
+      <c r="F56" t="s">
+        <v>276</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3656E94C-E294-4647-98EF-9C8CCDA1EFB6}">
+  <dimension ref="A1:F62"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="43.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="64.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>8</v>
+      </c>
       <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
+        <v>257</v>
+      </c>
+      <c r="F2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" t="s">
+        <v>51</v>
+      </c>
+      <c r="F12" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" t="s">
+        <v>57</v>
+      </c>
+      <c r="F13" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14" t="s">
+        <v>61</v>
+      </c>
+      <c r="E14" t="s">
+        <v>62</v>
+      </c>
+      <c r="F14" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>68</v>
+      </c>
+      <c r="B15" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15" t="s">
+        <v>70</v>
+      </c>
+      <c r="E15" t="s">
+        <v>51</v>
+      </c>
+      <c r="F15" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>74</v>
+      </c>
+      <c r="B16" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" t="s">
+        <v>72</v>
+      </c>
+      <c r="D16" t="s">
+        <v>71</v>
+      </c>
+      <c r="E16" t="s">
+        <v>73</v>
+      </c>
+      <c r="F16" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>78</v>
+      </c>
+      <c r="B17" t="s">
+        <v>77</v>
+      </c>
+      <c r="D17" t="s">
+        <v>79</v>
+      </c>
+      <c r="E17" t="s">
+        <v>79</v>
+      </c>
+      <c r="F17" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>86</v>
+      </c>
+      <c r="B18" t="s">
+        <v>82</v>
+      </c>
+      <c r="C18" t="s">
+        <v>84</v>
+      </c>
+      <c r="D18" t="s">
+        <v>83</v>
+      </c>
+      <c r="E18" t="s">
+        <v>85</v>
+      </c>
+      <c r="F18" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>88</v>
+      </c>
+      <c r="B19" t="s">
+        <v>87</v>
+      </c>
+      <c r="C19" t="s">
+        <v>89</v>
+      </c>
+      <c r="D19" t="s">
+        <v>90</v>
+      </c>
+      <c r="E19" t="s">
+        <v>91</v>
+      </c>
+      <c r="F19" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>95</v>
+      </c>
+      <c r="B20" t="s">
+        <v>94</v>
+      </c>
+      <c r="C20" t="s">
+        <v>96</v>
+      </c>
+      <c r="D20" t="s">
+        <v>96</v>
+      </c>
+      <c r="E20" t="s">
+        <v>96</v>
+      </c>
+      <c r="F20" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" t="s">
+        <v>98</v>
+      </c>
+      <c r="D21" t="s">
+        <v>105</v>
+      </c>
+      <c r="E21" t="s">
+        <v>99</v>
+      </c>
+      <c r="F21" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" t="s">
+        <v>26</v>
+      </c>
+      <c r="D22" t="s">
+        <v>104</v>
+      </c>
+      <c r="E22" t="s">
+        <v>102</v>
+      </c>
+      <c r="F22" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1</v>
+      </c>
+      <c r="C23" t="s">
+        <v>108</v>
+      </c>
+      <c r="D23" t="s">
+        <v>103</v>
+      </c>
+      <c r="E23" t="s">
+        <v>106</v>
+      </c>
+      <c r="F23" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" t="s">
+        <v>136</v>
+      </c>
+      <c r="D24" t="s">
+        <v>137</v>
+      </c>
+      <c r="E24" t="s">
+        <v>138</v>
+      </c>
+      <c r="F24" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C25" t="s">
+        <v>111</v>
+      </c>
+      <c r="D25" t="s">
+        <v>139</v>
+      </c>
+      <c r="E25" t="s">
+        <v>140</v>
+      </c>
+      <c r="F25" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C26" t="s">
+        <v>112</v>
+      </c>
+      <c r="D26" t="s">
+        <v>141</v>
+      </c>
+      <c r="E26" t="s">
+        <v>142</v>
+      </c>
+      <c r="F26" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1</v>
+      </c>
+      <c r="C27" t="s">
+        <v>113</v>
+      </c>
+      <c r="D27" t="s">
+        <v>149</v>
+      </c>
+      <c r="E27" t="s">
+        <v>148</v>
+      </c>
+      <c r="F27" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" t="s">
+        <v>114</v>
+      </c>
+      <c r="D28" t="s">
+        <v>151</v>
+      </c>
+      <c r="E28" t="s">
+        <v>152</v>
+      </c>
+      <c r="F28" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" t="s">
+        <v>1</v>
+      </c>
+      <c r="C29" t="s">
+        <v>115</v>
+      </c>
+      <c r="D29" t="s">
+        <v>155</v>
+      </c>
+      <c r="E29" t="s">
+        <v>156</v>
+      </c>
+      <c r="F29" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" t="s">
+        <v>1</v>
+      </c>
+      <c r="C30" t="s">
+        <v>109</v>
+      </c>
+      <c r="D30" t="s">
+        <v>107</v>
+      </c>
+      <c r="E30" t="s">
+        <v>110</v>
+      </c>
+      <c r="F30" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1</v>
+      </c>
+      <c r="C31" t="s">
+        <v>116</v>
+      </c>
+      <c r="D31" t="s">
+        <v>158</v>
+      </c>
+      <c r="E31" t="s">
+        <v>159</v>
+      </c>
+      <c r="F31" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" t="s">
+        <v>1</v>
+      </c>
+      <c r="C32" t="s">
+        <v>117</v>
+      </c>
+      <c r="D32" t="s">
+        <v>161</v>
+      </c>
+      <c r="E32" t="s">
+        <v>162</v>
+      </c>
+      <c r="F32" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C33" t="s">
+        <v>118</v>
+      </c>
+      <c r="D33" t="s">
+        <v>164</v>
+      </c>
+      <c r="E33" t="s">
+        <v>165</v>
+      </c>
+      <c r="F33" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C34" t="s">
+        <v>119</v>
+      </c>
+      <c r="D34" t="s">
+        <v>167</v>
+      </c>
+      <c r="E34" t="s">
+        <v>168</v>
+      </c>
+      <c r="F34" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>9</v>
+      </c>
+      <c r="B35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C35" t="s">
+        <v>120</v>
+      </c>
+      <c r="D35" t="s">
+        <v>170</v>
+      </c>
+      <c r="E35" t="s">
+        <v>171</v>
+      </c>
+      <c r="F35" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1</v>
+      </c>
+      <c r="C36" t="s">
+        <v>121</v>
+      </c>
+      <c r="D36" t="s">
+        <v>173</v>
+      </c>
+      <c r="E36" t="s">
+        <v>174</v>
+      </c>
+      <c r="F36" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1</v>
+      </c>
+      <c r="C37" t="s">
+        <v>122</v>
+      </c>
+      <c r="D37" t="s">
+        <v>176</v>
+      </c>
+      <c r="E37" t="s">
+        <v>177</v>
+      </c>
+      <c r="F37" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>9</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1</v>
+      </c>
+      <c r="C38" t="s">
+        <v>123</v>
+      </c>
+      <c r="D38" t="s">
+        <v>179</v>
+      </c>
+      <c r="E38" t="s">
+        <v>180</v>
+      </c>
+      <c r="F38" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>9</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C39" t="s">
+        <v>124</v>
+      </c>
+      <c r="D39" t="s">
+        <v>182</v>
+      </c>
+      <c r="E39" t="s">
+        <v>183</v>
+      </c>
+      <c r="F39" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>9</v>
+      </c>
+      <c r="B40" t="s">
+        <v>1</v>
+      </c>
+      <c r="C40" t="s">
+        <v>125</v>
+      </c>
+      <c r="D40" t="s">
+        <v>185</v>
+      </c>
+      <c r="E40" t="s">
+        <v>186</v>
+      </c>
+      <c r="F40" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>9</v>
+      </c>
+      <c r="B41" t="s">
+        <v>1</v>
+      </c>
+      <c r="C41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D41" t="s">
+        <v>188</v>
+      </c>
+      <c r="E41" t="s">
+        <v>189</v>
+      </c>
+      <c r="F41" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>9</v>
+      </c>
+      <c r="B42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C42" t="s">
+        <v>127</v>
+      </c>
+      <c r="D42" t="s">
+        <v>191</v>
+      </c>
+      <c r="E42" t="s">
+        <v>192</v>
+      </c>
+      <c r="F42" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>9</v>
+      </c>
+      <c r="B43" t="s">
+        <v>1</v>
+      </c>
+      <c r="C43" t="s">
+        <v>128</v>
+      </c>
+      <c r="D43" t="s">
+        <v>194</v>
+      </c>
+      <c r="E43" t="s">
+        <v>195</v>
+      </c>
+      <c r="F43" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>9</v>
+      </c>
+      <c r="B44" t="s">
+        <v>1</v>
+      </c>
+      <c r="C44" t="s">
+        <v>129</v>
+      </c>
+      <c r="D44" t="s">
+        <v>197</v>
+      </c>
+      <c r="E44" t="s">
+        <v>198</v>
+      </c>
+      <c r="F44" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>9</v>
+      </c>
+      <c r="B45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C45" t="s">
+        <v>130</v>
+      </c>
+      <c r="D45" t="s">
+        <v>200</v>
+      </c>
+      <c r="E45" t="s">
+        <v>201</v>
+      </c>
+      <c r="F45" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>9</v>
+      </c>
+      <c r="B46" t="s">
+        <v>1</v>
+      </c>
+      <c r="C46" t="s">
+        <v>131</v>
+      </c>
+      <c r="D46" t="s">
+        <v>203</v>
+      </c>
+      <c r="E46" t="s">
+        <v>204</v>
+      </c>
+      <c r="F46" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>9</v>
+      </c>
+      <c r="B47" t="s">
+        <v>1</v>
+      </c>
+      <c r="C47" t="s">
+        <v>132</v>
+      </c>
+      <c r="D47" t="s">
+        <v>206</v>
+      </c>
+      <c r="E47" t="s">
+        <v>207</v>
+      </c>
+      <c r="F47" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B48" t="s">
+        <v>1</v>
+      </c>
+      <c r="C48" t="s">
+        <v>133</v>
+      </c>
+      <c r="D48" t="s">
+        <v>209</v>
+      </c>
+      <c r="E48" t="s">
+        <v>210</v>
+      </c>
+      <c r="F48" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>9</v>
+      </c>
+      <c r="B49" t="s">
+        <v>1</v>
+      </c>
+      <c r="C49" t="s">
+        <v>134</v>
+      </c>
+      <c r="D49" t="s">
+        <v>212</v>
+      </c>
+      <c r="E49" t="s">
+        <v>213</v>
+      </c>
+      <c r="F49" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>9</v>
+      </c>
+      <c r="B50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C50" t="s">
+        <v>135</v>
+      </c>
+      <c r="D50" t="s">
+        <v>215</v>
+      </c>
+      <c r="E50" t="s">
+        <v>216</v>
+      </c>
+      <c r="F50" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>218</v>
+      </c>
+      <c r="B51" t="s">
+        <v>217</v>
+      </c>
+      <c r="C51" t="s">
+        <v>226</v>
+      </c>
+      <c r="D51" t="s">
+        <v>219</v>
+      </c>
+      <c r="E51" t="s">
+        <v>220</v>
+      </c>
+      <c r="F51" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>223</v>
+      </c>
+      <c r="B52" t="s">
+        <v>224</v>
+      </c>
+      <c r="C52" t="s">
+        <v>225</v>
+      </c>
+      <c r="D52" t="s">
+        <v>228</v>
+      </c>
+      <c r="E52" t="s">
+        <v>227</v>
+      </c>
+      <c r="F52" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>229</v>
+      </c>
+      <c r="B53" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" t="s">
+        <v>64</v>
+      </c>
+      <c r="D53" t="s">
+        <v>65</v>
+      </c>
+      <c r="E53" t="s">
+        <v>66</v>
+      </c>
+      <c r="F53" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>232</v>
+      </c>
+      <c r="B54" t="s">
+        <v>233</v>
+      </c>
+      <c r="C54" t="s">
+        <v>235</v>
+      </c>
+      <c r="D54" t="s">
+        <v>234</v>
+      </c>
+      <c r="E54" t="s">
+        <v>234</v>
+      </c>
+      <c r="F54" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>250</v>
+      </c>
+      <c r="B55" t="s">
+        <v>249</v>
+      </c>
+      <c r="C55" t="s">
+        <v>248</v>
+      </c>
+      <c r="D55" t="s">
+        <v>247</v>
+      </c>
+      <c r="E55" t="s">
+        <v>246</v>
+      </c>
+      <c r="F55" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>253</v>
+      </c>
+      <c r="B56" t="s">
+        <v>252</v>
+      </c>
+      <c r="C56" t="s">
+        <v>255</v>
+      </c>
+      <c r="D56" t="s">
+        <v>254</v>
+      </c>
+      <c r="E56" t="s">
+        <v>256</v>
+      </c>
+      <c r="F56" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>42</v>
+      </c>
+      <c r="B57" t="s">
+        <v>41</v>
+      </c>
+      <c r="C57" t="s">
+        <v>43</v>
+      </c>
+      <c r="D57" t="s">
+        <v>260</v>
+      </c>
+      <c r="E57" t="s">
+        <v>259</v>
+      </c>
+      <c r="F57" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>262</v>
+      </c>
+      <c r="B58" t="s">
+        <v>263</v>
+      </c>
+      <c r="C58" t="s">
+        <v>265</v>
+      </c>
+      <c r="D58" t="s">
+        <v>264</v>
+      </c>
+      <c r="E58" t="s">
+        <v>264</v>
+      </c>
+      <c r="F58" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>267</v>
+      </c>
+      <c r="B59" t="s">
+        <v>268</v>
+      </c>
+      <c r="C59" t="s">
+        <v>269</v>
+      </c>
+      <c r="F59" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>240</v>
+      </c>
+      <c r="B60" t="s">
+        <v>239</v>
+      </c>
+      <c r="C60" t="s">
+        <v>238</v>
+      </c>
+      <c r="D60" t="s">
+        <v>237</v>
+      </c>
+      <c r="E60" t="s">
+        <v>236</v>
+      </c>
+      <c r="F60" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>273</v>
+      </c>
+      <c r="B61" t="s">
+        <v>272</v>
+      </c>
+      <c r="C61" t="s">
+        <v>275</v>
+      </c>
+      <c r="D61" t="s">
+        <v>274</v>
+      </c>
+      <c r="E61" t="s">
+        <v>274</v>
+      </c>
+      <c r="F61" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>243</v>
+      </c>
+      <c r="B62" t="s">
+        <v>242</v>
+      </c>
+      <c r="C62" t="s">
+        <v>241</v>
+      </c>
+      <c r="D62" t="s">
+        <v>244</v>
+      </c>
+      <c r="E62" t="s">
+        <v>244</v>
+      </c>
+      <c r="F62" t="s">
+        <v>276</v>
       </c>
     </row>
   </sheetData>

--- a/data/datasets.xlsx
+++ b/data/datasets.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kokul/Projects/GOMAP-enrich/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90B9C563-4FEC-264F-AA4F-C56A553031A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{268C94C9-4725-3E46-A47C-69EE8E0127C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{E467A60D-F69A-4F4A-9E6E-FC569BD129C9}"/>
+    <workbookView xWindow="15120" yWindow="760" windowWidth="15120" windowHeight="18880" xr2:uid="{E467A60D-F69A-4F4A-9E6E-FC569BD129C9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="278">
   <si>
     <t>Species</t>
   </si>
@@ -868,6 +868,9 @@
   </si>
   <si>
     <t>Wild_Tomato_SGN_LA716_June_2023_v2.r1.gaf.gz</t>
+  </si>
+  <si>
+    <t>CSS_ChrLev_20200506</t>
   </si>
 </sst>
 </file>
@@ -2305,6 +2308,12 @@
       <c r="C53" t="s">
         <v>269</v>
       </c>
+      <c r="D53" t="s">
+        <v>277</v>
+      </c>
+      <c r="E53" t="s">
+        <v>277</v>
+      </c>
       <c r="F53" t="s">
         <v>266</v>
       </c>
